--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y871"/>
+  <dimension ref="A1:Y874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50877,14 +50877,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 54112-2023</t>
+          <t>A 54115-2023</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -50934,14 +50934,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 54115-2023</t>
+          <t>A 54112-2023</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51053,14 +51053,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 55042-2023</t>
+          <t>A 55045-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>14.4</v>
+        <v>20.5</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -51115,14 +51115,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 55045-2023</t>
+          <t>A 55042-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>20.5</v>
+        <v>14.4</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 57973-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51700,14 +51700,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 57973-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51888,7 +51888,7 @@
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -52002,7 +52002,7 @@
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,13 +52247,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F861" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G861" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52290,14 +52285,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52309,8 +52304,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G862" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52580,14 +52580,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52825,67 +52825,248 @@
       </c>
       <c r="R870" s="2" t="inlineStr"/>
     </row>
-    <row r="871">
+    <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G871" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H871" t="n">
+        <v>0</v>
+      </c>
+      <c r="I871" t="n">
+        <v>0</v>
+      </c>
+      <c r="J871" t="n">
+        <v>0</v>
+      </c>
+      <c r="K871" t="n">
+        <v>0</v>
+      </c>
+      <c r="L871" t="n">
+        <v>0</v>
+      </c>
+      <c r="M871" t="n">
+        <v>0</v>
+      </c>
+      <c r="N871" t="n">
+        <v>0</v>
+      </c>
+      <c r="O871" t="n">
+        <v>0</v>
+      </c>
+      <c r="P871" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q871" t="n">
+        <v>0</v>
+      </c>
+      <c r="R871" s="2" t="inlineStr"/>
+    </row>
+    <row r="872" ht="15" customHeight="1">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>A 60167-2023</t>
+        </is>
+      </c>
+      <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>HAGFORS</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
+      <c r="C872" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G872" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H872" t="n">
+        <v>0</v>
+      </c>
+      <c r="I872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J872" t="n">
+        <v>0</v>
+      </c>
+      <c r="K872" t="n">
+        <v>0</v>
+      </c>
+      <c r="L872" t="n">
+        <v>0</v>
+      </c>
+      <c r="M872" t="n">
+        <v>0</v>
+      </c>
+      <c r="N872" t="n">
+        <v>0</v>
+      </c>
+      <c r="O872" t="n">
+        <v>0</v>
+      </c>
+      <c r="P872" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q872" t="n">
+        <v>0</v>
+      </c>
+      <c r="R872" s="2" t="inlineStr"/>
+    </row>
+    <row r="873" ht="15" customHeight="1">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>A 60178-2023</t>
+        </is>
+      </c>
+      <c r="B873" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C873" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="G871" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H871" t="n">
-        <v>0</v>
-      </c>
-      <c r="I871" t="n">
-        <v>0</v>
-      </c>
-      <c r="J871" t="n">
-        <v>0</v>
-      </c>
-      <c r="K871" t="n">
-        <v>0</v>
-      </c>
-      <c r="L871" t="n">
-        <v>0</v>
-      </c>
-      <c r="M871" t="n">
-        <v>0</v>
-      </c>
-      <c r="N871" t="n">
-        <v>0</v>
-      </c>
-      <c r="O871" t="n">
-        <v>0</v>
-      </c>
-      <c r="P871" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q871" t="n">
-        <v>0</v>
-      </c>
-      <c r="R871" s="2" t="inlineStr"/>
+      <c r="G873" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H873" t="n">
+        <v>0</v>
+      </c>
+      <c r="I873" t="n">
+        <v>0</v>
+      </c>
+      <c r="J873" t="n">
+        <v>0</v>
+      </c>
+      <c r="K873" t="n">
+        <v>0</v>
+      </c>
+      <c r="L873" t="n">
+        <v>0</v>
+      </c>
+      <c r="M873" t="n">
+        <v>0</v>
+      </c>
+      <c r="N873" t="n">
+        <v>0</v>
+      </c>
+      <c r="O873" t="n">
+        <v>0</v>
+      </c>
+      <c r="P873" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q873" t="n">
+        <v>0</v>
+      </c>
+      <c r="R873" s="2" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>A 60221-2023</t>
+        </is>
+      </c>
+      <c r="B874" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C874" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G874" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H874" t="n">
+        <v>0</v>
+      </c>
+      <c r="I874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J874" t="n">
+        <v>0</v>
+      </c>
+      <c r="K874" t="n">
+        <v>0</v>
+      </c>
+      <c r="L874" t="n">
+        <v>0</v>
+      </c>
+      <c r="M874" t="n">
+        <v>0</v>
+      </c>
+      <c r="N874" t="n">
+        <v>0</v>
+      </c>
+      <c r="O874" t="n">
+        <v>0</v>
+      </c>
+      <c r="P874" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q874" t="n">
+        <v>0</v>
+      </c>
+      <c r="R874" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51650,7 +51650,7 @@
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51881,14 +51881,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -52002,7 +52002,7 @@
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,8 +52247,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G861" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52285,14 +52290,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52304,13 +52309,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F862" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G862" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52580,14 +52580,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52649,7 +52649,7 @@
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52897,7 +52897,7 @@
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52947,14 +52947,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53009,14 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y874"/>
+  <dimension ref="A1:Y875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50877,14 +50877,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 54115-2023</t>
+          <t>A 54112-2023</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -50934,14 +50934,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 54112-2023</t>
+          <t>A 54115-2023</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51053,14 +51053,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 55045-2023</t>
+          <t>A 55048-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -51115,14 +51115,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 55042-2023</t>
+          <t>A 55045-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>14.4</v>
+        <v>20.5</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -51177,14 +51177,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 55048-2023</t>
+          <t>A 55042-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51415,14 +51415,14 @@
     <row r="847" ht="15" customHeight="1">
       <c r="A847" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B847" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 57973-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51700,14 +51700,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 57973-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -51764,7 +51764,7 @@
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51838,13 +51838,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G854" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51881,14 +51876,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51901,7 +51896,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51933,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51957,8 +51952,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G856" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,13 +52247,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F861" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G861" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52290,14 +52285,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52309,8 +52304,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G862" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,8 +52542,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G866" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52580,14 +52585,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52599,13 +52604,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G867" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52711,7 +52711,7 @@
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52890,14 +52890,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 60167-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52909,8 +52909,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -52947,14 +52952,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60167-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52966,13 +52971,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F873" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G873" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53006,17 +53006,17 @@
       </c>
       <c r="R873" s="2" t="inlineStr"/>
     </row>
-    <row r="874">
+    <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53067,6 +53067,63 @@
         <v>0</v>
       </c>
       <c r="R874" s="2" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>A 60664-2023</t>
+        </is>
+      </c>
+      <c r="B875" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="C875" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G875" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H875" t="n">
+        <v>0</v>
+      </c>
+      <c r="I875" t="n">
+        <v>0</v>
+      </c>
+      <c r="J875" t="n">
+        <v>0</v>
+      </c>
+      <c r="K875" t="n">
+        <v>0</v>
+      </c>
+      <c r="L875" t="n">
+        <v>0</v>
+      </c>
+      <c r="M875" t="n">
+        <v>0</v>
+      </c>
+      <c r="N875" t="n">
+        <v>0</v>
+      </c>
+      <c r="O875" t="n">
+        <v>0</v>
+      </c>
+      <c r="P875" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q875" t="n">
+        <v>0</v>
+      </c>
+      <c r="R875" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y875"/>
+  <dimension ref="A1:Y877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50877,14 +50877,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 54112-2023</t>
+          <t>A 54115-2023</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -50934,14 +50934,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 54115-2023</t>
+          <t>A 54112-2023</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51115,14 +51115,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 55045-2023</t>
+          <t>A 55042-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>20.5</v>
+        <v>14.4</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -51177,14 +51177,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 55042-2023</t>
+          <t>A 55045-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>14.4</v>
+        <v>20.5</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51415,14 +51415,14 @@
     <row r="847" ht="15" customHeight="1">
       <c r="A847" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B847" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51593,7 +51593,7 @@
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51838,8 +51838,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G854" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51876,14 +51881,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51896,7 +51901,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51933,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51952,13 +51957,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F856" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G856" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52585,14 +52585,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52604,8 +52604,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G867" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52647,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52661,13 +52666,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G868" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52711,7 +52711,7 @@
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52890,14 +52890,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60167-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52909,13 +52909,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G872" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -52952,14 +52947,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60167-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52971,8 +52966,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G873" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53016,7 +53016,7 @@
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
       </c>
       <c r="R874" s="2" t="inlineStr"/>
     </row>
-    <row r="875">
+    <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
           <t>A 60664-2023</t>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53124,6 +53124,125 @@
         <v>0</v>
       </c>
       <c r="R875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876" ht="15" customHeight="1">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>A 61025-2023</t>
+        </is>
+      </c>
+      <c r="B876" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C876" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G876" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H876" t="n">
+        <v>0</v>
+      </c>
+      <c r="I876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J876" t="n">
+        <v>0</v>
+      </c>
+      <c r="K876" t="n">
+        <v>0</v>
+      </c>
+      <c r="L876" t="n">
+        <v>0</v>
+      </c>
+      <c r="M876" t="n">
+        <v>0</v>
+      </c>
+      <c r="N876" t="n">
+        <v>0</v>
+      </c>
+      <c r="O876" t="n">
+        <v>0</v>
+      </c>
+      <c r="P876" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q876" t="n">
+        <v>0</v>
+      </c>
+      <c r="R876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>A 61140-2023</t>
+        </is>
+      </c>
+      <c r="B877" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C877" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G877" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L877" t="n">
+        <v>0</v>
+      </c>
+      <c r="M877" t="n">
+        <v>0</v>
+      </c>
+      <c r="N877" t="n">
+        <v>0</v>
+      </c>
+      <c r="O877" t="n">
+        <v>0</v>
+      </c>
+      <c r="P877" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q877" t="n">
+        <v>0</v>
+      </c>
+      <c r="R877" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51053,14 +51053,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 55048-2023</t>
+          <t>A 55042-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -51115,14 +51115,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 55042-2023</t>
+          <t>A 55045-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>14.4</v>
+        <v>20.5</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -51177,14 +51177,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 55045-2023</t>
+          <t>A 55048-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 57973-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 57973-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51700,14 +51700,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51776,13 +51776,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F853" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G853" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51819,14 +51814,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51844,7 +51839,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51881,14 +51876,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51900,8 +51895,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G855" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52947,14 +52947,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53009,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51053,14 +51053,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 55042-2023</t>
+          <t>A 55045-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>14.4</v>
+        <v>20.5</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -51115,14 +51115,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 55045-2023</t>
+          <t>A 55048-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -51177,14 +51177,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 55048-2023</t>
+          <t>A 55042-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>16.5</v>
+        <v>14.4</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51415,14 +51415,14 @@
     <row r="847" ht="15" customHeight="1">
       <c r="A847" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B847" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 57973-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51700,14 +51700,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 57973-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -51764,7 +51764,7 @@
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51814,14 +51814,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51876,14 +51876,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,13 +52542,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F866" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G866" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52585,14 +52580,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52610,7 +52605,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52647,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52666,8 +52661,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G868" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y877"/>
+  <dimension ref="A1:Y882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51776,8 +51776,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G853" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51814,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51839,7 +51844,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51876,14 +51881,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51895,13 +51900,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G855" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,8 +52247,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G861" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52285,14 +52290,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52304,13 +52309,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F862" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G862" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52354,7 +52354,7 @@
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52642,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52890,14 +52890,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 60167-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52909,8 +52909,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -52947,14 +52952,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60167-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52966,13 +52971,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F873" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G873" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53009,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
       </c>
       <c r="R876" s="2" t="inlineStr"/>
     </row>
-    <row r="877">
+    <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
           <t>A 61140-2023</t>
@@ -53197,7 +53197,7 @@
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53243,6 +53243,296 @@
         <v>0</v>
       </c>
       <c r="R877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878" ht="15" customHeight="1">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>A 61238-2023</t>
+        </is>
+      </c>
+      <c r="B878" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C878" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G878" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H878" t="n">
+        <v>0</v>
+      </c>
+      <c r="I878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J878" t="n">
+        <v>0</v>
+      </c>
+      <c r="K878" t="n">
+        <v>0</v>
+      </c>
+      <c r="L878" t="n">
+        <v>0</v>
+      </c>
+      <c r="M878" t="n">
+        <v>0</v>
+      </c>
+      <c r="N878" t="n">
+        <v>0</v>
+      </c>
+      <c r="O878" t="n">
+        <v>0</v>
+      </c>
+      <c r="P878" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q878" t="n">
+        <v>0</v>
+      </c>
+      <c r="R878" s="2" t="inlineStr"/>
+    </row>
+    <row r="879" ht="15" customHeight="1">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>A 61311-2023</t>
+        </is>
+      </c>
+      <c r="B879" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C879" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G879" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H879" t="n">
+        <v>0</v>
+      </c>
+      <c r="I879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J879" t="n">
+        <v>0</v>
+      </c>
+      <c r="K879" t="n">
+        <v>0</v>
+      </c>
+      <c r="L879" t="n">
+        <v>0</v>
+      </c>
+      <c r="M879" t="n">
+        <v>0</v>
+      </c>
+      <c r="N879" t="n">
+        <v>0</v>
+      </c>
+      <c r="O879" t="n">
+        <v>0</v>
+      </c>
+      <c r="P879" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q879" t="n">
+        <v>0</v>
+      </c>
+      <c r="R879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880" ht="15" customHeight="1">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>A 61315-2023</t>
+        </is>
+      </c>
+      <c r="B880" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C880" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G880" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J880" t="n">
+        <v>0</v>
+      </c>
+      <c r="K880" t="n">
+        <v>0</v>
+      </c>
+      <c r="L880" t="n">
+        <v>0</v>
+      </c>
+      <c r="M880" t="n">
+        <v>0</v>
+      </c>
+      <c r="N880" t="n">
+        <v>0</v>
+      </c>
+      <c r="O880" t="n">
+        <v>0</v>
+      </c>
+      <c r="P880" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q880" t="n">
+        <v>0</v>
+      </c>
+      <c r="R880" s="2" t="inlineStr"/>
+    </row>
+    <row r="881" ht="15" customHeight="1">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>A 61287-2023</t>
+        </is>
+      </c>
+      <c r="B881" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C881" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G881" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H881" t="n">
+        <v>0</v>
+      </c>
+      <c r="I881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J881" t="n">
+        <v>0</v>
+      </c>
+      <c r="K881" t="n">
+        <v>0</v>
+      </c>
+      <c r="L881" t="n">
+        <v>0</v>
+      </c>
+      <c r="M881" t="n">
+        <v>0</v>
+      </c>
+      <c r="N881" t="n">
+        <v>0</v>
+      </c>
+      <c r="O881" t="n">
+        <v>0</v>
+      </c>
+      <c r="P881" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q881" t="n">
+        <v>0</v>
+      </c>
+      <c r="R881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>A 61304-2023</t>
+        </is>
+      </c>
+      <c r="B882" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C882" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G882" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L882" t="n">
+        <v>0</v>
+      </c>
+      <c r="M882" t="n">
+        <v>0</v>
+      </c>
+      <c r="N882" t="n">
+        <v>0</v>
+      </c>
+      <c r="O882" t="n">
+        <v>0</v>
+      </c>
+      <c r="P882" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q882" t="n">
+        <v>0</v>
+      </c>
+      <c r="R882" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y882"/>
+  <dimension ref="A1:Y883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51415,14 +51415,14 @@
     <row r="847" ht="15" customHeight="1">
       <c r="A847" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B847" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51593,7 +51593,7 @@
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51881,14 +51881,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58437-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,13 +52247,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F861" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G861" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52290,14 +52285,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58518-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52310,7 +52305,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52347,14 +52342,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 58437-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52366,8 +52361,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G863" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -52404,14 +52404,14 @@
     <row r="864" ht="15" customHeight="1">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A 58518-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B864" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,8 +52542,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G866" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52580,14 +52585,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52599,13 +52604,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G867" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52897,7 +52897,7 @@
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53128,14 +53128,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 61025-2023</t>
+          <t>A 61140-2023</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53147,13 +53147,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G876" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53190,14 +53185,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 61140-2023</t>
+          <t>A 61025-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53209,8 +53204,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G877" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53254,7 +53254,7 @@
         <v>45264</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45264</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53423,14 +53423,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 61287-2023</t>
+          <t>A 61304-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53477,62 +53477,124 @@
       </c>
       <c r="R881" s="2" t="inlineStr"/>
     </row>
-    <row r="882">
+    <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 61304-2023</t>
+          <t>A 61287-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C882" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G882" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L882" t="n">
+        <v>0</v>
+      </c>
+      <c r="M882" t="n">
+        <v>0</v>
+      </c>
+      <c r="N882" t="n">
+        <v>0</v>
+      </c>
+      <c r="O882" t="n">
+        <v>0</v>
+      </c>
+      <c r="P882" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q882" t="n">
+        <v>0</v>
+      </c>
+      <c r="R882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>A 61641-2023</t>
+        </is>
+      </c>
+      <c r="B883" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E882" t="inlineStr">
-        <is>
-          <t>HAGFORS</t>
-        </is>
-      </c>
-      <c r="G882" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H882" t="n">
-        <v>0</v>
-      </c>
-      <c r="I882" t="n">
-        <v>0</v>
-      </c>
-      <c r="J882" t="n">
-        <v>0</v>
-      </c>
-      <c r="K882" t="n">
-        <v>0</v>
-      </c>
-      <c r="L882" t="n">
-        <v>0</v>
-      </c>
-      <c r="M882" t="n">
-        <v>0</v>
-      </c>
-      <c r="N882" t="n">
-        <v>0</v>
-      </c>
-      <c r="O882" t="n">
-        <v>0</v>
-      </c>
-      <c r="P882" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q882" t="n">
-        <v>0</v>
-      </c>
-      <c r="R882" s="2" t="inlineStr"/>
+      <c r="C883" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G883" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H883" t="n">
+        <v>0</v>
+      </c>
+      <c r="I883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J883" t="n">
+        <v>0</v>
+      </c>
+      <c r="K883" t="n">
+        <v>0</v>
+      </c>
+      <c r="L883" t="n">
+        <v>0</v>
+      </c>
+      <c r="M883" t="n">
+        <v>0</v>
+      </c>
+      <c r="N883" t="n">
+        <v>0</v>
+      </c>
+      <c r="O883" t="n">
+        <v>0</v>
+      </c>
+      <c r="P883" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q883" t="n">
+        <v>0</v>
+      </c>
+      <c r="R883" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y883"/>
+  <dimension ref="A1:Y886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51776,13 +51776,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F853" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G853" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51819,14 +51814,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51844,7 +51839,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51881,14 +51876,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51900,8 +51895,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G855" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51945,7 +51945,7 @@
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52228,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58437-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,8 +52247,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G861" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52285,14 +52290,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58518-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52305,7 +52310,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52342,14 +52347,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58437-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52361,13 +52366,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F863" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G863" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -52404,14 +52404,14 @@
     <row r="864" ht="15" customHeight="1">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58518-2023</t>
         </is>
       </c>
       <c r="B864" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,13 +52542,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F866" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G866" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52585,14 +52580,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52604,8 +52599,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G867" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52704,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52773,7 +52773,7 @@
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52890,14 +52890,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60167-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52909,13 +52909,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G872" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -52952,14 +52947,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60167-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52971,8 +52966,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G873" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53009,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>45264</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53309,14 +53309,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 61311-2023</t>
+          <t>A 61304-2023</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -53366,14 +53366,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 61315-2023</t>
+          <t>A 61311-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -53423,14 +53423,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 61304-2023</t>
+          <t>A 61315-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53487,7 +53487,7 @@
         <v>45264</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
       </c>
       <c r="R882" s="2" t="inlineStr"/>
     </row>
-    <row r="883">
+    <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
           <t>A 61641-2023</t>
@@ -53544,7 +53544,7 @@
         <v>45265</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53595,6 +53595,187 @@
         <v>0</v>
       </c>
       <c r="R883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884" ht="15" customHeight="1">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>A 61992-2023</t>
+        </is>
+      </c>
+      <c r="B884" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C884" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G884" t="n">
+        <v>4</v>
+      </c>
+      <c r="H884" t="n">
+        <v>0</v>
+      </c>
+      <c r="I884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L884" t="n">
+        <v>0</v>
+      </c>
+      <c r="M884" t="n">
+        <v>0</v>
+      </c>
+      <c r="N884" t="n">
+        <v>0</v>
+      </c>
+      <c r="O884" t="n">
+        <v>0</v>
+      </c>
+      <c r="P884" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q884" t="n">
+        <v>0</v>
+      </c>
+      <c r="R884" s="2" t="inlineStr"/>
+    </row>
+    <row r="885" ht="15" customHeight="1">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>A 61818-2023</t>
+        </is>
+      </c>
+      <c r="B885" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C885" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="G885" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H885" t="n">
+        <v>0</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J885" t="n">
+        <v>0</v>
+      </c>
+      <c r="K885" t="n">
+        <v>0</v>
+      </c>
+      <c r="L885" t="n">
+        <v>0</v>
+      </c>
+      <c r="M885" t="n">
+        <v>0</v>
+      </c>
+      <c r="N885" t="n">
+        <v>0</v>
+      </c>
+      <c r="O885" t="n">
+        <v>0</v>
+      </c>
+      <c r="P885" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q885" t="n">
+        <v>0</v>
+      </c>
+      <c r="R885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>A 61964-2023</t>
+        </is>
+      </c>
+      <c r="B886" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C886" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G886" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H886" t="n">
+        <v>0</v>
+      </c>
+      <c r="I886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J886" t="n">
+        <v>0</v>
+      </c>
+      <c r="K886" t="n">
+        <v>0</v>
+      </c>
+      <c r="L886" t="n">
+        <v>0</v>
+      </c>
+      <c r="M886" t="n">
+        <v>0</v>
+      </c>
+      <c r="N886" t="n">
+        <v>0</v>
+      </c>
+      <c r="O886" t="n">
+        <v>0</v>
+      </c>
+      <c r="P886" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q886" t="n">
+        <v>0</v>
+      </c>
+      <c r="R886" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51757,14 +51757,14 @@
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 57276-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51776,8 +51776,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G853" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -51814,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51833,13 +51838,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G854" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51876,14 +51876,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 57276-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51895,13 +51895,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G855" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51938,14 +51933,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51958,7 +51953,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51995,14 +51990,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52014,8 +52009,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G857" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52059,7 +52059,7 @@
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58437-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52185,13 +52185,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F860" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G860" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52228,14 +52223,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58518-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52247,13 +52242,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F861" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G861" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52290,14 +52280,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52309,8 +52299,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G862" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52347,14 +52342,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 58437-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52366,8 +52361,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G863" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -52404,14 +52404,14 @@
     <row r="864" ht="15" customHeight="1">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A 58518-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B864" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,8 +52542,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G866" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52580,14 +52585,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52605,7 +52610,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52642,14 +52647,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52667,7 +52672,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52704,14 +52709,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52729,7 +52734,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52766,14 +52771,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52785,13 +52790,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F870" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G870" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52897,7 +52897,7 @@
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52947,14 +52947,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53009,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53128,14 +53128,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 61140-2023</t>
+          <t>A 61025-2023</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53147,8 +53147,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G876" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53185,14 +53190,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 61025-2023</t>
+          <t>A 61140-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53204,13 +53209,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G877" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53254,7 +53254,7 @@
         <v>45264</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53309,14 +53309,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 61304-2023</t>
+          <t>A 61311-2023</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -53366,14 +53366,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 61311-2023</t>
+          <t>A 61315-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -53423,14 +53423,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 61315-2023</t>
+          <t>A 61304-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53487,7 +53487,7 @@
         <v>45264</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53544,7 +53544,7 @@
         <v>45265</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53599,14 +53599,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 61992-2023</t>
+          <t>A 61818-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53618,13 +53618,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F884" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G884" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53661,14 +53656,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 61818-2023</t>
+          <t>A 61992-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53680,8 +53675,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G885" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -53725,7 +53725,7 @@
         <v>45266</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y886"/>
+  <dimension ref="A1:Y887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>43431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>43431</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>43437</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>43438</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>43438</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>43444</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>43446</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>43446</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>43446</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>43469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>43474</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>43479</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>43479</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43481</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43481</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43486</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43487</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43488</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43489</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43490</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43500</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43508</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43516</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43516</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43523</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43523</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43534</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43541</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43544</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43546</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43549</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>43551</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43558</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43560</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43565</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43565</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43565</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43572</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43578</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43585</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43585</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43587</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43591</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43591</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43591</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43598</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43598</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43608</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43608</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43612</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>43612</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43619</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43626</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>43630</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43633</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43633</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43649</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43651</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43654</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43654</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43664</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>43689</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>43693</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43697</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43705</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>43710</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43712</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43714</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43725</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43725</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>43727</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>43732</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>43738</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43738</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43740</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43752</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43752</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43752</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43752</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43753</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43753</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43761</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>43761</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43762</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>43762</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43775</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43781</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43795</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43795</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>43795</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>43795</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>43801</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43802</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43804</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43804</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43829</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>43837</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>43837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>43845</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43851</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43853</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43857</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43865</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>43869</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43869</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43875</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>43878</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43882</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>43886</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>43887</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>43887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43902</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43910</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43910</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43913</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43913</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43916</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43917</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>43917</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43921</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43921</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43927</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43929</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>43938</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43944</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43944</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43944</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>43949</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>43962</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43962</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43965</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43966</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43966</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>43966</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>43976</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43978</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>43994</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>43997</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43999</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44000</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44000</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44011</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44012</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44012</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44018</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44022</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44047</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44047</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44047</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44067</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44070</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44083</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44085</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44085</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44096</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44101</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44103</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44103</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44110</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44110</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44110</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44110</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44113</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44119</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44119</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44123</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44130</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44132</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44137</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44144</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44145</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44153</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44161</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44161</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44161</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44161</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44167</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44167</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44167</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44207</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44214</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44216</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44217</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44221</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44221</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44225</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44241</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44241</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44241</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44245</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44252</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44256</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44257</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44266</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44273</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44284</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44284</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44308</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44309</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44316</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44320</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44323</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44323</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44323</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44325</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44326</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44327</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44328</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44337</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44337</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44341</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44343</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44351</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44357</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44357</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44362</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44364</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44364</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44379</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44393</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44400</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44405</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44417</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44417</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44417</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44420</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44421</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44421</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44424</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44424</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44425</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44426</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44428</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44432</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44433</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44434</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44434</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44435</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44438</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44439</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44439</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44449</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44449</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44452</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44452</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44455</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44459</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44465</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44465</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44465</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44465</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44469</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44469</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44479</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44488</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44491</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44491</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44491</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44499</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44501</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44502</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44510</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44510</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44515</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44515</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44516</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44516</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44516</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44517</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44526</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44526</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44529</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44537</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44537</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>44538</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44538</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44540</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44540</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44545</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44545</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>44545</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44545</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44547</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44550</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44564</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44565</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44566</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44566</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44566</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44567</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44571</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44579</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44582</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44582</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44584</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44587</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44587</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44594</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44594</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>44595</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44596</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44602</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44603</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44603</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44606</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44606</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44606</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44606</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>44606</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44607</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44610</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44613</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>44613</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44622</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44622</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44624</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44628</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44628</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44634</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44635</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44638</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44649</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44649</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44649</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44649</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44649</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44663</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44664</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44664</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44664</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44665</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44678</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44679</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44683</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44683</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44683</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44685</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44687</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44687</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44687</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44694</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44694</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44697</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44699</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44700</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44706</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44706</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44711</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44712</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44719</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44722</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44725</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44725</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44739</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44742</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44743</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44749</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44749</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44753</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44754</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44755</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44756</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>44757</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44757</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44760</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44762</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44762</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44762</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44763</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44763</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44763</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44763</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44770</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44770</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44770</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>44776</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44781</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44790</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44790</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44791</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44791</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44799</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44799</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44802</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44803</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44805</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44805</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44805</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44806</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44809</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44810</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44812</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44817</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44817</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44817</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44817</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>44817</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44817</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>44817</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44824</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44825</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44830</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44832</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44832</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44832</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44834</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44834</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44836</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44839</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44844</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44848</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44851</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44852</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44852</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44853</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44858</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44858</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44860</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>44860</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44860</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44865</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44868</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44868</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44868</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44869</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44869</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44872</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44872</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44874</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44876</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44876</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44879</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44880</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44883</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44883</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44883</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44883</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44887</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>44889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44890</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44890</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44893</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44894</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>44896</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>44896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44896</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44901</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44901</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>44903</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44903</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44903</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44904</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44904</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44904</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44907</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44908</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44915</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44917</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44924</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>44924</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44924</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44928</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>44929</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44929</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44930</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>44937</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44937</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44937</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44938</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44941</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44946</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44949</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44949</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44950</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44950</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44950</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44951</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>44951</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44953</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>44959</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44959</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>44959</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44960</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>44965</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>44966</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44977</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44978</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44984</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44988</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44991</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44991</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44994</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44994</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>44998</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>44998</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45000</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45000</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45005</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45006</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45013</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45016</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45019</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45019</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45020</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45020</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45020</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45028</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45028</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45029</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45029</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45029</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45030</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45030</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45033</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45033</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45033</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45033</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45035</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45035</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45036</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45036</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45040</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45041</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45041</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45041</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45044</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45044</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45044</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45050</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45051</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45054</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45055</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45057</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45057</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45057</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45057</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45058</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45058</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45058</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45062</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45063</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45069</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45070</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45070</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45070</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45071</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45071</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45072</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45072</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45072</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45075</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45076</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45078</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>45078</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45078</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45079</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>45084</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45084</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45084</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45084</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45085</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45085</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45088</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45090</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45090</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45091</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45093</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45093</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45093</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45093</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45093</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45093</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45097</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45098</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45099</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45099</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45103</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45103</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45103</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45103</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45103</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45105</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45106</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45106</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45107</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45107</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45107</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45110</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45110</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45110</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45111</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45112</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45112</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45112</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45117</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45118</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45119</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45121</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45132</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45140</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45141</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45142</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45145</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45145</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45147</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45147</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45147</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45148</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45149</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45149</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45152</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45152</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45154</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45154</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45155</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45155</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45155</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45155</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45161</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>45162</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45162</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45163</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45163</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45163</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45166</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45166</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45166</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45169</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45170</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45172</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45174</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45175</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45181</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45182</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>45182</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45182</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45182</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45184</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45187</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45189</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45190</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45190</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45191</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45191</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45191</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45195</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45195</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45195</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45196</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45196</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45197</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45197</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>45197</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>45201</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45201</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45201</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45201</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45201</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45201</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45201</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45201</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45202</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45202</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45202</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45203</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45203</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45203</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45203</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45204</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45204</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45204</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>45205</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45209</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45209</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45211</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45211</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45211</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45211</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45211</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45212</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45212</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45212</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45216</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45216</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45216</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45217</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45217</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45217</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45217</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45217</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45219</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45219</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45219</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45219</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45219</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45219</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45219</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45224</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45224</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45226</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45226</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45226</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45226</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45226</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45226</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45226</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45229</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45229</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45230</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45231</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45232</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45232</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>45236</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45237</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45243</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45243</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45243</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51415,14 +51415,14 @@
     <row r="847" ht="15" customHeight="1">
       <c r="A847" t="inlineStr">
         <is>
-          <t>A 56808-2023</t>
+          <t>A 56893-2023</t>
         </is>
       </c>
       <c r="B847" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -51472,14 +51472,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 56884-2023</t>
+          <t>A 56888-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -51529,14 +51529,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 56895-2023</t>
+          <t>A 56808-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -51586,14 +51586,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 56893-2023</t>
+          <t>A 56884-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -51643,14 +51643,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 56888-2023</t>
+          <t>A 56895-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -51707,7 +51707,7 @@
         <v>45244</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45245</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51819,14 +51819,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 57164-2023</t>
+          <t>A 57241-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51838,8 +51838,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G854" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -51876,14 +51881,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 58242-2023</t>
+          <t>A 57164-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51896,7 +51901,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51933,14 +51938,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 58259-2023</t>
+          <t>A 58242-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51953,7 +51958,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51990,14 +51995,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 57241-2023</t>
+          <t>A 58254-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52009,13 +52014,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F857" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G857" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -52052,14 +52052,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 58254-2023</t>
+          <t>A 58259-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -52116,7 +52116,7 @@
         <v>45246</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52166,14 +52166,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 58437-2023</t>
+          <t>A 58276-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52185,8 +52185,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G860" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -52223,14 +52228,14 @@
     <row r="861" ht="15" customHeight="1">
       <c r="A861" t="inlineStr">
         <is>
-          <t>A 58518-2023</t>
+          <t>A 58307-2023</t>
         </is>
       </c>
       <c r="B861" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52242,8 +52247,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G861" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -52280,14 +52290,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 58276-2023</t>
+          <t>A 58312-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52299,13 +52309,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F862" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G862" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -52342,14 +52347,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 58307-2023</t>
+          <t>A 58437-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52361,13 +52366,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F863" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G863" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -52404,14 +52404,14 @@
     <row r="864" ht="15" customHeight="1">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A 58312-2023</t>
+          <t>A 58518-2023</t>
         </is>
       </c>
       <c r="B864" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -52468,7 +52468,7 @@
         <v>45252</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52523,14 +52523,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 59822-2023</t>
+          <t>A 59874-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52585,14 +52585,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 59899-2023</t>
+          <t>A 59735-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52604,13 +52604,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G867" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52647,14 +52642,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 59874-2023</t>
+          <t>A 59881-2023</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52672,7 +52667,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52709,14 +52704,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 59895-2023</t>
+          <t>A 59822-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52734,7 +52729,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -52771,14 +52766,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 59735-2023</t>
+          <t>A 59895-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52790,8 +52785,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G870" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -52828,14 +52828,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 59881-2023</t>
+          <t>A 59899-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -52890,14 +52890,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 60167-2023</t>
+          <t>A 60178-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52909,8 +52909,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G872" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -52947,14 +52952,14 @@
     <row r="873" ht="15" customHeight="1">
       <c r="A873" t="inlineStr">
         <is>
-          <t>A 60178-2023</t>
+          <t>A 60221-2023</t>
         </is>
       </c>
       <c r="B873" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52972,7 +52977,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -53009,14 +53014,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 60221-2023</t>
+          <t>A 60167-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53028,13 +53033,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F874" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G874" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53078,7 +53078,7 @@
         <v>45259</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45261</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45261</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53247,14 +53247,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 61238-2023</t>
+          <t>A 61287-2023</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53266,13 +53266,8 @@
           <t>HAGFORS</t>
         </is>
       </c>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G878" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -53309,14 +53304,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 61311-2023</t>
+          <t>A 61304-2023</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53329,7 +53324,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -53366,14 +53361,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 61315-2023</t>
+          <t>A 61311-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53386,7 +53381,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -53423,14 +53418,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 61304-2023</t>
+          <t>A 61315-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53443,7 +53438,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53480,14 +53475,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 61287-2023</t>
+          <t>A 61238-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53499,8 +53494,13 @@
           <t>HAGFORS</t>
         </is>
       </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G882" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53544,7 +53544,7 @@
         <v>45265</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45266</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45266</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53715,7 +53715,7 @@
       </c>
       <c r="R885" s="2" t="inlineStr"/>
     </row>
-    <row r="886">
+    <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
           <t>A 61964-2023</t>
@@ -53725,7 +53725,7 @@
         <v>45266</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53776,6 +53776,68 @@
         <v>0</v>
       </c>
       <c r="R886" s="2" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>A 62461-2023</t>
+        </is>
+      </c>
+      <c r="B887" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="C887" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>HAGFORS</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G887" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H887" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0</v>
+      </c>
+      <c r="J887" t="n">
+        <v>0</v>
+      </c>
+      <c r="K887" t="n">
+        <v>0</v>
+      </c>
+      <c r="L887" t="n">
+        <v>0</v>
+      </c>
+      <c r="M887" t="n">
+        <v>0</v>
+      </c>
+      <c r="N887" t="n">
+        <v>0</v>
+      </c>
+      <c r="O887" t="n">
+        <v>0</v>
+      </c>
+      <c r="P887" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q887" t="n">
+        <v>0</v>
+      </c>
+      <c r="R887" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAGFORS.xlsx
+++ b/Översikt HAGFORS.xlsx
@@ -564,7 +564,7 @@
         <v>44096</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45246</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45167</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>44445</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45173</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45036</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>44509</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>44566</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>43411</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43739</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>44096</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44438</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44532</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44603</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45188</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>43320</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>43341</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>43343</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>43356</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>43364</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>43381</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>43388</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>43402</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>43404</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>43404</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>43405</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>43409</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>43410</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>43416</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>43416</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>43418</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>43421</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>43424</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>43426</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>43426</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>43427</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>43427</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>43427</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270<